--- a/contagem_diaria_export.xlsx
+++ b/contagem_diaria_export.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -516,31 +516,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>1</v>
       </c>
@@ -551,57 +553,6 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
         <v>1</v>
       </c>
     </row>
